--- a/descriptive tables/desc_nonagri.xlsx
+++ b/descriptive tables/desc_nonagri.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="4">
+  <si>
+    <t xml:space="preserve">province</t>
+  </si>
   <si>
     <t xml:space="preserve">variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">province</t>
   </si>
   <si>
     <t xml:space="preserve">mean_value</t>
@@ -309,12 +309,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.04"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.6"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -323,72 +319,85 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" s="1" t="n">
-        <v>86542.9151943463</v>
+        <v>89668.7608695652</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C3" s="1" t="n">
-        <v>226629.910714286</v>
+        <v>87525.3115079365</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>115749.628571429</v>
+        <v>91598.5078416729</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C5" s="1" t="n">
-        <v>144332.0861678</v>
+        <v>172284.656652361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C6" s="1" t="n">
-        <v>119061.766937669</v>
+        <v>85162.3781818182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="n">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C7" s="1" t="n">
-        <v>112816.68</v>
+        <v>127149.918032787</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="n">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C8" s="1" t="n">
-        <v>51332.3624595469</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="1" t="n">
-        <v>0</v>
+        <v>94730.8759124088</v>
       </c>
     </row>
   </sheetData>
